--- a/partial/sliding_window_results_window_5.xlsx
+++ b/partial/sliding_window_results_window_5.xlsx
@@ -463,13 +463,13 @@
         <v>29.54</v>
       </c>
       <c r="C2" t="n">
-        <v>28.77159668602728</v>
+        <v>29.36188838516495</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.7684033139727191</v>
+        <v>-0.1781116148350463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5904436529242572</v>
+        <v>0.0317237473391479</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.55</v>
       </c>
       <c r="C3" t="n">
-        <v>29.90122115551857</v>
+        <v>29.78406929991331</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3512211555185694</v>
+        <v>0.2340692999133118</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1233563000837991</v>
+        <v>0.05478843716190792</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.75</v>
       </c>
       <c r="C4" t="n">
-        <v>29.66499987532517</v>
+        <v>29.73033275421328</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.08500012467483486</v>
+        <v>-0.01966724578672441</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007225021194737471</v>
+        <v>0.000386800556835429</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.84</v>
       </c>
       <c r="C5" t="n">
-        <v>30.5415314462977</v>
+        <v>30.29087302102019</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7015314462976967</v>
+        <v>0.4508730210201932</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4921463701445381</v>
+        <v>0.2032864810838756</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.81</v>
       </c>
       <c r="C6" t="n">
-        <v>30.41077861873373</v>
+        <v>30.16897008820004</v>
       </c>
       <c r="D6" t="n">
-        <v>0.600778618733731</v>
+        <v>0.3589700882000386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3609349487276097</v>
+        <v>0.1288595242223435</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>30.24578231115241</v>
+        <v>29.90822042436572</v>
       </c>
       <c r="D7" t="n">
-        <v>0.325782311152409</v>
+        <v>-0.01177957563428578</v>
       </c>
       <c r="E7" t="n">
-        <v>0.106134114259805</v>
+        <v>0.0001387584021238592</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.98</v>
       </c>
       <c r="C8" t="n">
-        <v>29.62150842841587</v>
+        <v>29.83849563355738</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3584915715841319</v>
+        <v>-0.1415043664426214</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1285162068968608</v>
+        <v>0.02002348572232769</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.04</v>
       </c>
       <c r="C9" t="n">
-        <v>29.90509423108006</v>
+        <v>29.84181641502009</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1349057689199356</v>
+        <v>-0.1981835849799047</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01819956648787905</v>
+        <v>0.03927673335548712</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.21</v>
       </c>
       <c r="C10" t="n">
-        <v>29.48238977579566</v>
+        <v>29.92971577386612</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7276102242043372</v>
+        <v>-0.2802842261338796</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5294166383666858</v>
+        <v>0.07855924741946775</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.22</v>
       </c>
       <c r="C11" t="n">
-        <v>29.87582778898143</v>
+        <v>30.09036226924875</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3441722110185665</v>
+        <v>-0.1296377307512451</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1184545108374087</v>
+        <v>0.01680594123433231</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.38</v>
       </c>
       <c r="C12" t="n">
-        <v>29.71312480306775</v>
+        <v>30.19173587840176</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6668751969322457</v>
+        <v>-0.188264121598241</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4447225282834215</v>
+        <v>0.03544337948115728</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.44</v>
       </c>
       <c r="C13" t="n">
-        <v>30.38637470091635</v>
+        <v>30.48602904936035</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.05362529908365588</v>
+        <v>0.04602904936034946</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002875672701811543</v>
+        <v>0.002118673385017487</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.48</v>
       </c>
       <c r="C14" t="n">
-        <v>30.35189786770854</v>
+        <v>30.3830970472716</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1281021322914597</v>
+        <v>-0.09690295272840288</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01641015629761865</v>
+        <v>0.009390182247483083</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.69</v>
       </c>
       <c r="C15" t="n">
-        <v>30.59799747773</v>
+        <v>30.40061040351136</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.09200252226999694</v>
+        <v>-0.2893895964886433</v>
       </c>
       <c r="E15" t="n">
-        <v>0.008464464104041284</v>
+        <v>0.08374633855585976</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.75</v>
       </c>
       <c r="C16" t="n">
-        <v>30.22668918367056</v>
+        <v>30.75093117328817</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5233108163294418</v>
+        <v>0.0009311732881656098</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2738542104873867</v>
+        <v>8.670836925931538e-07</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.94</v>
       </c>
       <c r="C17" t="n">
-        <v>30.66051695140128</v>
+        <v>30.80748496167179</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2794830485987241</v>
+        <v>-0.1325150383282079</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07811077445403676</v>
+        <v>0.0175602353831264</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.95</v>
       </c>
       <c r="C18" t="n">
-        <v>30.93097425548262</v>
+        <v>30.92476076942891</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01902574451737848</v>
+        <v>-0.02523923057109201</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0003619789544405575</v>
+        <v>0.0006370187598207454</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.02</v>
       </c>
       <c r="C19" t="n">
-        <v>31.52768362082061</v>
+        <v>31.14990447558944</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5076836208206146</v>
+        <v>0.1299044755894379</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2577426588495296</v>
+        <v>0.01687517277816685</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.12</v>
       </c>
       <c r="C20" t="n">
-        <v>31.8954276512661</v>
+        <v>31.28542580370341</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7754276512660958</v>
+        <v>0.1654258037034069</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6012880423480539</v>
+        <v>0.0273656965309181</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.28</v>
       </c>
       <c r="C21" t="n">
-        <v>32.01428376739394</v>
+        <v>31.1840818168263</v>
       </c>
       <c r="D21" t="n">
-        <v>0.73428376739394</v>
+        <v>-0.09591818317370127</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5391726510582378</v>
+        <v>0.009200297863343709</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.38</v>
       </c>
       <c r="C22" t="n">
-        <v>31.81616876501472</v>
+        <v>31.07793052009108</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4361687650147168</v>
+        <v>-0.3020694799089227</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1902431915744632</v>
+        <v>0.09124597069244708</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.58</v>
       </c>
       <c r="C23" t="n">
-        <v>32.19045575260361</v>
+        <v>31.27197894129191</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6104557526036132</v>
+        <v>-0.3080210587080927</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3726562258868438</v>
+        <v>0.09487697260765429</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.65</v>
       </c>
       <c r="C24" t="n">
-        <v>32.07760720707016</v>
+        <v>31.73957506555968</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4276072070701602</v>
+        <v>0.08957506555968564</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1828479235383429</v>
+        <v>0.008023692370021981</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.88</v>
       </c>
       <c r="C25" t="n">
-        <v>32.69388249805409</v>
+        <v>32.50872068394579</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8138824980540953</v>
+        <v>0.6287206839457902</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6624047206387744</v>
+        <v>0.3952896984212622</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.28</v>
       </c>
       <c r="C26" t="n">
-        <v>32.39883288137233</v>
+        <v>32.53122384196269</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1188328813723274</v>
+        <v>0.251223841962684</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01412125369524963</v>
+        <v>0.06311341877049162</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.45</v>
       </c>
       <c r="C27" t="n">
-        <v>32.50268193461038</v>
+        <v>32.88905978555466</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0526819346103764</v>
+        <v>0.4390597855546616</v>
       </c>
       <c r="E27" t="n">
-        <v>0.002775386234291975</v>
+        <v>0.1927734952913055</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.85</v>
       </c>
       <c r="C28" t="n">
-        <v>32.74211580690621</v>
+        <v>33.12466019119131</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1078841930937884</v>
+        <v>0.2746601911913089</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01163899911949782</v>
+        <v>0.07543822062524637</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.9</v>
       </c>
       <c r="C29" t="n">
-        <v>32.8855232564657</v>
+        <v>33.1876042672486</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.01447674353430273</v>
+        <v>0.2876042672486037</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0002095761033579758</v>
+        <v>0.08271621453960623</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.1</v>
       </c>
       <c r="C30" t="n">
-        <v>32.91331340906391</v>
+        <v>33.31342044662783</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1866865909360911</v>
+        <v>0.2134204466278291</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0348518832353394</v>
+        <v>0.04554828703882205</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.4</v>
       </c>
       <c r="C31" t="n">
-        <v>33.83299115305665</v>
+        <v>33.71395351623086</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4329911530566477</v>
+        <v>0.3139535162308604</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1874813386253253</v>
+        <v>0.09856681035372114</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.7</v>
       </c>
       <c r="C32" t="n">
-        <v>33.74871538907802</v>
+        <v>33.72374872713567</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0487153890780192</v>
+        <v>0.02374872713566845</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002373189133022792</v>
+        <v>0.0005640020405644348</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.1</v>
       </c>
       <c r="C33" t="n">
-        <v>33.8940528257012</v>
+        <v>33.79202561111252</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2059471742987995</v>
+        <v>-0.3079743888874802</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0424142386016601</v>
+        <v>0.09484822421061688</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.4</v>
       </c>
       <c r="C34" t="n">
-        <v>34.07701773910097</v>
+        <v>34.19723309020993</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3229822608990318</v>
+        <v>-0.2027669097900642</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1043175408554503</v>
+        <v>0.04111441970581203</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.9</v>
       </c>
       <c r="C35" t="n">
-        <v>34.6658757599753</v>
+        <v>34.41133269554031</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2341242400246983</v>
+        <v>-0.488667304459689</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05481415976714256</v>
+        <v>0.2387957344478984</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.3</v>
       </c>
       <c r="C36" t="n">
-        <v>35.7840420212037</v>
+        <v>35.51423373159818</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4840420212036989</v>
+        <v>0.2142337315981848</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2342966782909621</v>
+        <v>0.04589609175448309</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.7</v>
       </c>
       <c r="C37" t="n">
-        <v>36.19699942473285</v>
+        <v>35.77938616129119</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4969994247328486</v>
+        <v>0.07938616129118259</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2470084281847825</v>
+        <v>0.006302162604549657</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.3</v>
       </c>
       <c r="C38" t="n">
-        <v>36.38994972819609</v>
+        <v>36.05415544559393</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08994972819608904</v>
+        <v>-0.2458445544060694</v>
       </c>
       <c r="E38" t="n">
-        <v>0.008090953602550296</v>
+        <v>0.06043954493111884</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.8</v>
       </c>
       <c r="C39" t="n">
-        <v>36.97987452478498</v>
+        <v>36.66889473158334</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1798745247849851</v>
+        <v>-0.131105268416654</v>
       </c>
       <c r="E39" t="n">
-        <v>0.03235484466662422</v>
+        <v>0.0171885914066029</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.3</v>
       </c>
       <c r="C40" t="n">
-        <v>37.02470801298504</v>
+        <v>36.75928092501331</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2752919870149526</v>
+        <v>-0.5407190749866899</v>
       </c>
       <c r="E40" t="n">
-        <v>0.07578567811464083</v>
+        <v>0.2923771180544616</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.9</v>
       </c>
       <c r="C41" t="n">
-        <v>37.96974537549301</v>
+        <v>37.85027403718746</v>
       </c>
       <c r="D41" t="n">
-        <v>0.06974537549300663</v>
+        <v>-0.04972596281253772</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00486441740266049</v>
+        <v>0.002472671377633884</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.5</v>
       </c>
       <c r="C42" t="n">
-        <v>38.60573691186258</v>
+        <v>38.61013807581099</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1057369118625786</v>
+        <v>0.110138075810994</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01118029453023472</v>
+        <v>0.01213039574334826</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.9</v>
       </c>
       <c r="C43" t="n">
-        <v>39.01080985958171</v>
+        <v>39.00815598828223</v>
       </c>
       <c r="D43" t="n">
-        <v>0.110809859581714</v>
+        <v>0.1081559882822347</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01227882498051917</v>
+        <v>0.01169771780130689</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.4</v>
       </c>
       <c r="C44" t="n">
-        <v>39.42546228338429</v>
+        <v>39.39532542033854</v>
       </c>
       <c r="D44" t="n">
-        <v>0.02546228338429302</v>
+        <v>-0.004674579661461564</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0006483278751420442</v>
+        <v>2.185169501135011e-05</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.9</v>
       </c>
       <c r="C45" t="n">
-        <v>39.7220449143099</v>
+        <v>39.65916224730229</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.177955085690094</v>
+        <v>-0.2408377526977077</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0316680125229687</v>
+        <v>0.0580028231244822</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.1</v>
       </c>
       <c r="C46" t="n">
-        <v>39.88261139275777</v>
+        <v>39.93191622206452</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2173886072422349</v>
+        <v>-0.1680837779354789</v>
       </c>
       <c r="E46" t="n">
-        <v>0.04725780655871865</v>
+        <v>0.02825215640506339</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.6</v>
       </c>
       <c r="C47" t="n">
-        <v>40.06105682113947</v>
+        <v>40.14516499738765</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5389431788605279</v>
+        <v>-0.4548350026123487</v>
       </c>
       <c r="E47" t="n">
-        <v>0.290459750040291</v>
+        <v>0.2068748796013752</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.9</v>
       </c>
       <c r="C48" t="n">
-        <v>40.36163272153543</v>
+        <v>40.46227174547302</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5383672784645697</v>
+        <v>-0.4377282545269807</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2898393265213475</v>
+        <v>0.1916060248112372</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.2</v>
       </c>
       <c r="C49" t="n">
-        <v>41.31439799775037</v>
+        <v>41.57788098621841</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1143979977503662</v>
+        <v>0.3778809862184076</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01308690188929279</v>
+        <v>0.1427940397453964</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.5</v>
       </c>
       <c r="C50" t="n">
-        <v>41.49454877040444</v>
+        <v>41.69234694904898</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.00545122959555755</v>
+        <v>0.1923469490489822</v>
       </c>
       <c r="E50" t="n">
-        <v>2.971590410348253e-05</v>
+        <v>0.03699734880845176</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.8</v>
       </c>
       <c r="C51" t="n">
-        <v>42.02650361853983</v>
+        <v>42.12059394226941</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2265036185398372</v>
+        <v>0.3205939422694115</v>
       </c>
       <c r="E51" t="n">
-        <v>0.05130388921164011</v>
+        <v>0.1027804758198428</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.835059353520354</v>
+        <v>-0.3595455662107803</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>7.9111339447674</v>
+        <v>3.51493607336627</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.158222678895348</v>
+        <v>0.07029872146732541</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_5.xlsx
+++ b/partial/sliding_window_results_window_5.xlsx
@@ -463,13 +463,13 @@
         <v>29.54</v>
       </c>
       <c r="C2" t="n">
-        <v>29.36188838516495</v>
+        <v>28.94622255988387</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1781116148350463</v>
+        <v>-0.5937774401161278</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0317237473391479</v>
+        <v>0.3525716483908617</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.55</v>
       </c>
       <c r="C3" t="n">
-        <v>29.78406929991331</v>
+        <v>29.6094854299225</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2340692999133118</v>
+        <v>0.05948542992249983</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05478843716190792</v>
+        <v>0.003538516373064638</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.75</v>
       </c>
       <c r="C4" t="n">
-        <v>29.73033275421328</v>
+        <v>29.56120525548962</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01966724578672441</v>
+        <v>-0.1887947445103784</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000386800556835429</v>
+        <v>0.03564345555473904</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.84</v>
       </c>
       <c r="C5" t="n">
-        <v>30.29087302102019</v>
+        <v>30.08834634040456</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4508730210201932</v>
+        <v>0.2483463404045558</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2032864810838756</v>
+        <v>0.06167590479233552</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.81</v>
       </c>
       <c r="C6" t="n">
-        <v>30.16897008820004</v>
+        <v>29.96630417414248</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3589700882000386</v>
+        <v>0.1563041741424769</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1288595242223435</v>
+        <v>0.02443099485436174</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>29.90822042436572</v>
+        <v>29.93496378058057</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01177957563428578</v>
+        <v>0.01496378058056891</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001387584021238592</v>
+        <v>0.0002239147292634112</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>29.98</v>
       </c>
       <c r="C8" t="n">
-        <v>29.83849563355738</v>
+        <v>29.68220524715557</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1415043664426214</v>
+        <v>-0.2977947528444354</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02002348572232769</v>
+        <v>0.08868171482167833</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.04</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84181641502009</v>
+        <v>29.91942311637418</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1981835849799047</v>
+        <v>-0.1205768836258159</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03927673335548712</v>
+        <v>0.01453878486491354</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.21</v>
       </c>
       <c r="C10" t="n">
-        <v>29.92971577386612</v>
+        <v>29.84444176465734</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2802842261338796</v>
+        <v>-0.3655582353426645</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07855924741946775</v>
+        <v>0.1336328234268429</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.22</v>
       </c>
       <c r="C11" t="n">
-        <v>30.09036226924875</v>
+        <v>30.07085133047605</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1296377307512451</v>
+        <v>-0.1491486695239495</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01680594123433231</v>
+        <v>0.02224532562076429</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.38</v>
       </c>
       <c r="C12" t="n">
-        <v>30.19173587840176</v>
+        <v>30.14449416124753</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.188264121598241</v>
+        <v>-0.2355058387524736</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03544337948115728</v>
+        <v>0.05546300008650607</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.44</v>
       </c>
       <c r="C13" t="n">
-        <v>30.48602904936035</v>
+        <v>30.56377186233319</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04602904936034946</v>
+        <v>0.1237718623331894</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002118673385017487</v>
+        <v>0.01531947390542598</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.48</v>
       </c>
       <c r="C14" t="n">
-        <v>30.3830970472716</v>
+        <v>30.39156778052075</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09690295272840288</v>
+        <v>-0.08843221947925173</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009390182247483083</v>
+        <v>0.007820257442026548</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.69</v>
       </c>
       <c r="C15" t="n">
-        <v>30.40061040351136</v>
+        <v>30.44760193710786</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2893895964886433</v>
+        <v>-0.2423980628921392</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08374633855585976</v>
+        <v>0.05875682089386145</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.75</v>
       </c>
       <c r="C16" t="n">
-        <v>30.75093117328817</v>
+        <v>30.54119945276208</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0009311732881656098</v>
+        <v>-0.2088005472379209</v>
       </c>
       <c r="E16" t="n">
-        <v>8.670836925931538e-07</v>
+        <v>0.04359766852685522</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.94</v>
       </c>
       <c r="C17" t="n">
-        <v>30.80748496167179</v>
+        <v>30.59999269372442</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1325150383282079</v>
+        <v>-0.3400073062755844</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0175602353831264</v>
+        <v>0.1156049683207791</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>30.95</v>
       </c>
       <c r="C18" t="n">
-        <v>30.92476076942891</v>
+        <v>30.71309445577057</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.02523923057109201</v>
+        <v>-0.2369055442294261</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0006370187598207454</v>
+        <v>0.05612423688664057</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.02</v>
       </c>
       <c r="C19" t="n">
-        <v>31.14990447558944</v>
+        <v>31.05375640662432</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1299044755894379</v>
+        <v>0.03375640662432033</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01687517277816685</v>
+        <v>0.001139494988186458</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.12</v>
       </c>
       <c r="C20" t="n">
-        <v>31.28542580370341</v>
+        <v>31.28278435740969</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1654258037034069</v>
+        <v>0.1627843574096843</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0273656965309181</v>
+        <v>0.02649874701728385</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.28</v>
       </c>
       <c r="C21" t="n">
-        <v>31.1840818168263</v>
+        <v>31.31875516294957</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09591818317370127</v>
+        <v>0.03875516294956682</v>
       </c>
       <c r="E21" t="n">
-        <v>0.009200297863343709</v>
+        <v>0.001501962655247477</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.38</v>
       </c>
       <c r="C22" t="n">
-        <v>31.07793052009108</v>
+        <v>31.31234775375689</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3020694799089227</v>
+        <v>-0.06765224624310662</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09124597069244708</v>
+        <v>0.004576826421737934</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.58</v>
       </c>
       <c r="C23" t="n">
-        <v>31.27197894129191</v>
+        <v>31.60951736486901</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3080210587080927</v>
+        <v>0.02951736486901169</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09487697260765429</v>
+        <v>0.0008712748288103653</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.65</v>
       </c>
       <c r="C24" t="n">
-        <v>31.73957506555968</v>
+        <v>31.52362737722168</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08957506555968564</v>
+        <v>-0.1263726227783231</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008023692370021981</v>
+        <v>0.01597003978787234</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>31.88</v>
       </c>
       <c r="C25" t="n">
-        <v>32.50872068394579</v>
+        <v>32.07085104964037</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6287206839457902</v>
+        <v>0.1908510496403686</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3952896984212622</v>
+        <v>0.03642412314883044</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.28</v>
       </c>
       <c r="C26" t="n">
-        <v>32.53122384196269</v>
+        <v>31.99815484704363</v>
       </c>
       <c r="D26" t="n">
-        <v>0.251223841962684</v>
+        <v>-0.2818451529563681</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06311341877049162</v>
+        <v>0.07943669024499855</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.45</v>
       </c>
       <c r="C27" t="n">
-        <v>32.88905978555466</v>
+        <v>32.25947507436365</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4390597855546616</v>
+        <v>-0.1905249256363533</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1927734952913055</v>
+        <v>0.03629974728873794</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.85</v>
       </c>
       <c r="C28" t="n">
-        <v>33.12466019119131</v>
+        <v>32.93023633955124</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2746601911913089</v>
+        <v>0.08023633955124154</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07543822062524637</v>
+        <v>0.006437870184582127</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>32.9</v>
       </c>
       <c r="C29" t="n">
-        <v>33.1876042672486</v>
+        <v>33.08353469019088</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2876042672486037</v>
+        <v>0.1835346901908821</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08271621453960623</v>
+        <v>0.03368498250346307</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.1</v>
       </c>
       <c r="C30" t="n">
-        <v>33.31342044662783</v>
+        <v>32.97286166876292</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2134204466278291</v>
+        <v>-0.1271383312370844</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04554828703882205</v>
+        <v>0.01616415526975059</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.4</v>
       </c>
       <c r="C31" t="n">
-        <v>33.71395351623086</v>
+        <v>33.60642716644276</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3139535162308604</v>
+        <v>0.206427166442765</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09856681035372114</v>
+        <v>0.04261217504558902</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>33.7</v>
       </c>
       <c r="C32" t="n">
-        <v>33.72374872713567</v>
+        <v>33.49137642913883</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02374872713566845</v>
+        <v>-0.208623570861171</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0005640020405644348</v>
+        <v>0.04352379431886604</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.1</v>
       </c>
       <c r="C33" t="n">
-        <v>33.79202561111252</v>
+        <v>33.72213589363577</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3079743888874802</v>
+        <v>-0.3778641063642283</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09484822421061688</v>
+        <v>0.1427812828784368</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.4</v>
       </c>
       <c r="C34" t="n">
-        <v>34.19723309020993</v>
+        <v>34.1382772365737</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2027669097900642</v>
+        <v>-0.2617227634262989</v>
       </c>
       <c r="E34" t="n">
-        <v>0.04111441970581203</v>
+        <v>0.06849880489549839</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>34.9</v>
       </c>
       <c r="C35" t="n">
-        <v>34.41133269554031</v>
+        <v>34.77242045161046</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.488667304459689</v>
+        <v>-0.1275795483895408</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2387957344478984</v>
+        <v>0.01627654116727918</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.3</v>
       </c>
       <c r="C36" t="n">
-        <v>35.51423373159818</v>
+        <v>35.4721283341111</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2142337315981848</v>
+        <v>0.1721283341111004</v>
       </c>
       <c r="E36" t="n">
-        <v>0.04589609175448309</v>
+        <v>0.02962816340386261</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>35.7</v>
       </c>
       <c r="C37" t="n">
-        <v>35.77938616129119</v>
+        <v>35.73070285018812</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07938616129118259</v>
+        <v>0.03070285018811347</v>
       </c>
       <c r="E37" t="n">
-        <v>0.006302162604549657</v>
+        <v>0.0009426650096737395</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.3</v>
       </c>
       <c r="C38" t="n">
-        <v>36.05415544559393</v>
+        <v>36.24455340973244</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2458445544060694</v>
+        <v>-0.05544659026755738</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06043954493111884</v>
+        <v>0.003074324372298389</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>36.8</v>
       </c>
       <c r="C39" t="n">
-        <v>36.66889473158334</v>
+        <v>36.70947774200621</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.131105268416654</v>
+        <v>-0.09052225799378277</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0171885914066029</v>
+        <v>0.008194279192292969</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.3</v>
       </c>
       <c r="C40" t="n">
-        <v>36.75928092501331</v>
+        <v>36.87647507577982</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5407190749866899</v>
+        <v>-0.4235249242201746</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2923771180544616</v>
+        <v>0.1793733614357046</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>37.9</v>
       </c>
       <c r="C41" t="n">
-        <v>37.85027403718746</v>
+        <v>37.66453575940342</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.04972596281253772</v>
+        <v>-0.2354642405965777</v>
       </c>
       <c r="E41" t="n">
-        <v>0.002472671377633884</v>
+        <v>0.05544340859972301</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.5</v>
       </c>
       <c r="C42" t="n">
-        <v>38.61013807581099</v>
+        <v>38.4464684146862</v>
       </c>
       <c r="D42" t="n">
-        <v>0.110138075810994</v>
+        <v>-0.05353158531379876</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01213039574334826</v>
+        <v>0.002865630626208515</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>38.9</v>
       </c>
       <c r="C43" t="n">
-        <v>39.00815598828223</v>
+        <v>38.89044569832318</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1081559882822347</v>
+        <v>-0.009554301676821808</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01169771780130689</v>
+        <v>9.128468053172001e-05</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.4</v>
       </c>
       <c r="C44" t="n">
-        <v>39.39532542033854</v>
+        <v>39.29696629783321</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.004674579661461564</v>
+        <v>-0.1030337021667904</v>
       </c>
       <c r="E44" t="n">
-        <v>2.185169501135011e-05</v>
+        <v>0.01061594378219487</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>39.9</v>
       </c>
       <c r="C45" t="n">
-        <v>39.65916224730229</v>
+        <v>39.77431122548442</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2408377526977077</v>
+        <v>-0.1256887745155737</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0580028231244822</v>
+        <v>0.01579766803922673</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.1</v>
       </c>
       <c r="C46" t="n">
-        <v>39.93191622206452</v>
+        <v>39.79810840580336</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1680837779354789</v>
+        <v>-0.3018915941966398</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02825215640506339</v>
+        <v>0.09113853464658864</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.6</v>
       </c>
       <c r="C47" t="n">
-        <v>40.14516499738765</v>
+        <v>39.9820787409019</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4548350026123487</v>
+        <v>-0.6179212590980967</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2068748796013752</v>
+        <v>0.3818266824453772</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>40.9</v>
       </c>
       <c r="C48" t="n">
-        <v>40.46227174547302</v>
+        <v>40.29689079825238</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4377282545269807</v>
+        <v>-0.6031092017476141</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1916060248112372</v>
+        <v>0.3637407092326442</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.2</v>
       </c>
       <c r="C49" t="n">
-        <v>41.57788098621841</v>
+        <v>41.70852063806183</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3778809862184076</v>
+        <v>0.5085206380618246</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1427940397453964</v>
+        <v>0.2585932393348052</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.5</v>
       </c>
       <c r="C50" t="n">
-        <v>41.69234694904898</v>
+        <v>41.60935076459542</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1923469490489822</v>
+        <v>0.109350764595419</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03699734880845176</v>
+        <v>0.01195758971760275</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>41.8</v>
       </c>
       <c r="C51" t="n">
-        <v>42.12059394226941</v>
+        <v>41.84371609681255</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3205939422694115</v>
+        <v>0.04371609681255251</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1027804758198428</v>
+        <v>0.001911097120524464</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.3595455662107803</v>
+        <v>-5.063559135685928</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>3.51493607336627</v>
+        <v>3.07776260377535</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.07029872146732541</v>
+        <v>0.06155525207550701</v>
       </c>
     </row>
   </sheetData>
